--- a/jpcore-r4/feature/BodySiteに関するTerminologyの見直し/ValueSet-jp-imagingstudy-endoscopy-bodysite-vs.xlsx
+++ b/jpcore-r4/feature/BodySiteに関するTerminologyの見直し/ValueSet-jp-imagingstudy-endoscopy-bodysite-vs.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ImagingStudy_EndoScopy_BodySite_VS</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ImagingStudy_Endoscopy_BodySite_VS</t>
   </si>
   <si>
     <t>Version</t>
@@ -36,13 +36,13 @@
     <t>Name</t>
   </si>
   <si>
-    <t>JP_ImagingStudy_EndoScopy_BodySite_VS</t>
+    <t>JP_ImagingStudy_Endoscopy_BodySite_VS</t>
   </si>
   <si>
     <t>Title</t>
   </si>
   <si>
-    <t>JP Core ImagingStudy EndoScopy BodySite ValueSet</t>
+    <t>JP Core ImagingStudy Endoscopy BodySite ValueSet</t>
   </si>
   <si>
     <t>Status</t>
